--- a/tests/fixtures/test_cases/t101_fail_all.xlsx
+++ b/tests/fixtures/test_cases/t101_fail_all.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="data2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tbl_fail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,102 +438,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Indented</t>
-        </is>
+          <t xml:space="preserve">  Indented with spaces</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>SUM(B2:B10)</f>
+        <f>SUM(B2:B6)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Row1</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>100</v>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
+      <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="n"/>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Merged</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Note1|Note2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rate: %</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B1">
-        <f>RAND()</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Source: Test</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/tests/fixtures/test_cases/t101_fail_all.xlsx
+++ b/tests/fixtures/test_cases/t101_fail_all.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="tbl_fail" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,64 +440,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Indented with spaces</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
+          <t xml:space="preserve">  Indented</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>SUM(B2:B6)</f>
+        <f>SUM(B2:B10)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Row1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
       <c r="B5" s="1" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Merged</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Note1|Note2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Rate: %</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Taux</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1">
+        <f>RAND()</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Source: Test</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tests/fixtures/test_cases/t101_fail_all.xlsx
+++ b/tests/fixtures/test_cases/t101_fail_all.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="data2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tbl_fail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="tbl_fail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,51 +421,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t xml:space="preserve">  Category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Val</t>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Note col</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Indented</t>
-        </is>
+      <c r="A2">
+        <f>B2+B3</f>
+        <v/>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <f>SUM(B2:B10)</f>
-        <v/>
+      <c r="B3" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Row1</t>
-        </is>
-      </c>
       <c r="B4" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="1" t="n"/>
-    </row>
-    <row r="6"/>
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -478,31 +474,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="B1">
-        <f>RAND()</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -521,7 +492,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B2" t="n">
